--- a/Result/profitability/6151.xlsx
+++ b/Result/profitability/6151.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3475</v>
+        <v>0.4475</v>
       </c>
       <c r="N2" t="n">
-        <v>20.38875</v>
+        <v>21.40625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>0.34875</v>
+        <v>0.45875</v>
       </c>
       <c r="N3" t="n">
-        <v>19.80875</v>
+        <v>20.86875</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>0.57</v>
       </c>
       <c r="M4" t="n">
-        <v>0.38125</v>
+        <v>0.49</v>
       </c>
       <c r="N4" t="n">
-        <v>19.5875</v>
+        <v>20.43375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.47</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2825</v>
+        <v>0.38</v>
       </c>
       <c r="N5" t="n">
-        <v>17.3275</v>
+        <v>18.22625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>0.24875</v>
+        <v>0.35625</v>
       </c>
       <c r="N6" t="n">
-        <v>16.29625</v>
+        <v>17.15125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.61</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2837499999999999</v>
+        <v>0.4199999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>16.11875</v>
+        <v>16.85125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.77</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3674999999999999</v>
+        <v>0.42625</v>
       </c>
       <c r="N8" t="n">
-        <v>15.99875</v>
+        <v>16.4275</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6151</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>540</v>
+      </c>
+      <c r="D75" t="n">
+        <v>387</v>
+      </c>
+      <c r="E75" t="n">
+        <v>152</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.21</v>
+      </c>
+      <c r="G75" t="n">
+        <v>85</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.78%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>88</v>
+      </c>
+      <c r="K75" t="n">
+        <v>66</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.47125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>22.37125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6527777777777777</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1384180790960452</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.902439024390244</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.190000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.3420551855375833</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
